--- a/error_report.xlsx
+++ b/error_report.xlsx
@@ -54,12 +54,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -499,13 +499,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -518,16 +518,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -537,16 +537,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -575,16 +575,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -668,7 +668,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>borrowings</t>
+          <t>deferred_tax</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -678,18 +678,18 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Noncurrent Borrowings_Unsecured Loans_Loans and advances from others</t>
+          <t>Deferred Tax Assets (Net)_Deferred tax liabilities_Accumulated Depreciation</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1,487</t>
+          <t>1,12,897</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>153,154</t>
+          <t>148,154,143,184,142,145,168,139</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -709,35 +709,35 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>p222 Borrowings-Non-Current Unsecured 'Term Loans - from Others' non-current = 1,487; matches definition 'unsecured loans from non-bank parties' (judgment: term-loans-from-others = only unsecured-loans-from-others line disclosed)</t>
+          <t>p148 'Property, Plant and Equipment and ... 1,12,897'</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>consolidated_equity</t>
+          <t>deferred_tax</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Equity attributable to the equity holders of the parent</t>
+          <t>Deferred Tax Assets (Net)_Deferred tax liabilities_Accumulated Depreciation</t>
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>9,04,030</t>
+          <t>37,535</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>139,140,141,142,143,144</t>
+          <t>101,114,113,100,103,110,102,97</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>deferred_tax</t>
+          <t>finance_costs</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -770,18 +770,18 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Deferred Tax Assets (Net)_Deferred tax liabilities_Accumulated Depreciation</t>
+          <t>Interest Expense Borrowings</t>
         </is>
       </c>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,12,897</t>
+          <t>22,050</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>141,142,143,167,168,169</t>
+          <t>152,168,142,184,165,153,167,166</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -799,59 +799,59 @@
           <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>p148 'Property, Plant and Equipment and ... 1,12,897'</t>
-        </is>
-      </c>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>loans_advances</t>
+          <t>investments</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Short Term Loans And Advances_Other Deposit Assets</t>
+          <t>Non Current Investments_Unquoted Debentures/Bonds</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,472</t>
+          <t>1,084</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>1,105</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>147,148,149,143,144,145</t>
+          <t>104,105,106</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>false_positive</t>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
+          <t>Value mismatch — model extracted a different figure than the report</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>p127-128: unquoted debentures (excl subsidiaries) = JV-cos [BAM DLR Mumbai 40 + BAM DLR Network 2 + DXDC 63 = 105; Sintex Twenty Devind 900] + Other-co Mahan Energen 100 = 1,105. Prior GT 205 missed Sintex Twenty Devind 900</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -861,38 +861,42 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Short Term Loans And Advances_Other Deposit Assets</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n"/>
+          <t>Short Term Loans And Advances_Advances to related parties</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,403</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94,95,96,101,102,103</t>
+          <t>148,158,153,149,159,33,162,144</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -900,7 +904,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>other_cur_liabilities</t>
+          <t>loans_advances</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -910,18 +914,18 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Other Current Liabilities_Revenue received in advance</t>
+          <t>Short Term Loans And Advances_Other Deposit Assets</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,099</t>
+          <t>2,403</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113,114,115</t>
+          <t>95,120,108,113,121,33,110,109</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -949,23 +953,23 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CSR Expenditure</t>
+          <t>Legal &amp; Professional Charges</t>
         </is>
       </c>
       <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,223</t>
+          <t>3,874</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116,117,118</t>
+          <t>157,158,148,153,145,144,143,136</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -983,7 +987,11 @@
           <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>p157(pr.233): cons Other Expenses 'Professional Fees 3,874'</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -998,18 +1006,18 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Donations Subscriptions</t>
+          <t>CSR Expenditure</t>
         </is>
       </c>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,734</t>
+          <t>1,223</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>116,117,118</t>
+          <t>116,117</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1053,7 +1061,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116,117,118</t>
+          <t>116,117</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1090,10 +1098,14 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Other Noncurrent Liabilities_Other Long Term Liabilities</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n"/>
+          <t>Other Noncurrent Liabilities_Total Long Term Liabilities</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5,51,020</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>6,932</t>
@@ -1101,22 +1113,22 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>152,153,154,168,169,170</t>
+          <t>169,183,184,139,154,152,143,148</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1124,7 +1136,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>other_nc_liabilities</t>
+          <t>ppe</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1134,33 +1146,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Other Noncurrent Liabilities_Total Long Term Liabilities</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n"/>
+          <t>Accumulated Depreciation_Furnitures &amp; Fixtures</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13,287</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,932</t>
+          <t>6,717</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>152,153,154,168,169,170</t>
+          <t>146</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1178,168 +1194,40 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation_Furnitures &amp; Fixtures</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n"/>
+          <t>Accumulated Depreciation_Office Equipments</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>61,473</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,717</t>
+          <t>22,187</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>145,146,147,148</t>
+          <t>146</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>ppe</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation_Office Equipments</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>22,187</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>145,146,147,148</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>ppe</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Gross Carrying Value_Furnitures &amp; Fixtures</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>17,369</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>145,146,147,148</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>ppe</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Gross Carrying Value_Office Equipments</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>71,504</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>145,146,147,148</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1352,7 +1240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1447,7 +1335,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>286,287,288,289</t>
+          <t>288,289,287,167,286,247,273,268</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1455,7 +1343,7 @@
           <t>grounded</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>mismatch</t>
         </is>
@@ -1475,38 +1363,42 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Deferred Tax Liability (Net)_Deferred Tax Assets_Leave Encashment</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n"/>
+          <t>Deferred Tax Assets (Net)_Deferred tax liabilities_Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>(5,751)</t>
+        </is>
+      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>286,287,288,289</t>
+          <t>367,333,353,346,354,351,377,348</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -1514,7 +1406,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>deferred_tax</t>
+          <t>finance_costs</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1524,37 +1416,33 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Deferred Tax Assets (Net)_Deferred tax liabilities_Accumulated Depreciation</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>(5,751)</t>
-        </is>
-      </c>
+          <t>Interest Expense Borrowings</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>1,051</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>366,367,368,371,372,373</t>
+          <t>373,397,388,372,346,400,402,401</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>false_positive</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -1562,28 +1450,28 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>deferred_tax</t>
+          <t>investments</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Deferred Tax Liability (Net)_Deferred Tax Assets_Leave Encashment</t>
+          <t>Non Current Investments_Joint Venture/Partnerships</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>366,367,368,371,372,373</t>
+          <t>277,278,279</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1616,13 +1504,13 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Non Current Investments_Joint Venture/Partnerships</t>
+          <t>Non Current Investments_Unquoted Debentures/Bonds</t>
         </is>
       </c>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1655,38 +1543,42 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Non Current Investments_Unquoted Debentures/Bonds</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n"/>
+          <t>Non Current Investments_Joint Venture/Partnerships</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>277,278,279</t>
+          <t>357,358,359</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -1694,32 +1586,32 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>investments</t>
+          <t>loans_advances</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Non Current Investments_Joint Venture/Partnerships</t>
+          <t>Short Term Loans And Advances_Advances to related parties</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>357,358,359</t>
+          <t>278,322,284,238,330,290,285,316</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1729,12 +1621,12 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned a value but GT says '-' — not disclosed in the report</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -1742,7 +1634,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>loans_advances</t>
+          <t>other_cur_assets</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1752,33 +1644,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Short Term Loans And Advances_Advances to related parties</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n"/>
+          <t>Other Current Assets_Less : Doubtful Advances</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>(43)</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>(122)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>401,402,403,362,363,364</t>
+          <t>359,390,164,364,367,386,395,363</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -1786,7 +1682,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>other_cur_assets</t>
+          <t>other_cur_liabilities</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1796,18 +1692,18 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Other Current Assets_Less : Doubtful Advances</t>
+          <t>Other Current Liabilities_Revenue received in advance</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>(131)</t>
+          <t>358</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>283,284,285,289,290,291</t>
+          <t>313</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1830,7 +1726,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>other_cur_assets</t>
+          <t>other_cur_liabilities</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1840,33 +1736,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Other Current Assets_Advances given suppliers</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n"/>
+          <t>Other Current Liabilities_Accrued Salary Payable</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>389,390,391,358,359,360</t>
+          <t>385,390,374,382,377,383,371,370</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1874,28 +1774,28 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>other_cur_assets</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Other Current Assets_Less : Doubtful Advances</t>
+          <t>Carriage Outwards</t>
         </is>
       </c>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>(122)</t>
+          <t>8,062</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>389,390,391,358,359,360</t>
+          <t>316,330,290,247,291,297,286,273</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1918,28 +1818,28 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>other_cur_liabilities</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Other Current Liabilities_Revenue received in advance</t>
+          <t>Loss On Disposal Of Fixed Asset</t>
         </is>
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>(486)</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>384,385,386,389,390,391</t>
+          <t>316,330,290,247,291,297,286,273</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1972,18 +1872,18 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Impairment loss on financial assets loans and advances</t>
+          <t>Payment for reimbursement of expenses</t>
         </is>
       </c>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>315,316,317,289,290,291</t>
+          <t>316,330,290,247,291,297,286,273</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2016,18 +1916,18 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Loss On Disposal Of Fixed Asset</t>
+          <t>Total Power &amp; Fuel Expenses</t>
         </is>
       </c>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>(486)</t>
+          <t>14,396</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>315,316,317,289,290,291</t>
+          <t>316,330,290,247,291,297,286,273</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2055,38 +1955,42 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Payment for reimbursement of expenses</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n"/>
+          <t>CSR Expenditure</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>315,316,317,289,290,291</t>
+          <t>388,368,376,403,333,402,363,373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -2094,7 +1998,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>other_nc_liabilities</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -2104,33 +2008,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Payments To Auditor</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n"/>
+          <t>Other Noncurrent Liabilities_Other Long Term Liabilities</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1,685</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>315,316,317,289,290,291</t>
+          <t>325,295,329,257,326,313,289,270</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -2138,28 +2046,28 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>other_nc_liabilities</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Provision Bad Doubtful Loans Advances</t>
+          <t>Other Noncurrent Liabilities_Total Long Term Liabilities</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>967</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>315,316,317,289,290,291</t>
+          <t>367,396,403,372,397,401,343,351</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2182,43 +2090,47 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>ppe</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CSR Expenditure</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n"/>
+          <t>Gross Carrying Value_Office Equipments</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1,487</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>1,467</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>387,388,389,375,376,377</t>
+          <t>268</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>reconciled</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -2226,43 +2138,47 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>ppe</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Carriage Outwards</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n"/>
+          <t>Other CWIP</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>27,023</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,006</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>387,388,389,375,376,377</t>
+          <t>268</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>reconciled</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -2270,28 +2186,28 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Impairment loss on financial assets loans and advances</t>
+          <t>Equity Forfeited</t>
         </is>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>(546,249)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>387,388,389,375,376,377</t>
+          <t>222,223,224,290,291,292</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2309,48 +2225,56 @@
           <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>p292 'Less: Face Value of Equity Shares forfeited (546,249)'</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Payments To Auditor</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n"/>
+          <t>Equity Paid Up</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>222</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>387,388,389,375,376,377</t>
+          <t>222,223,224,290,291,292</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -2358,72 +2282,80 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Provision Bad Doubtful Loans Advances</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n"/>
+          <t>No Of Shares bought back or treasury shares</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>(10,466,985)</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>(26,783,115)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>387,388,389,375,376,377</t>
+          <t>222,223,224,290,291,292</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr"/>
+          <t>Value mismatch — model extracted a different figure than the report</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>p369 Less: Treasury Shares = (b)(i) 16,316,130 + (b)(ii) 10,466,985 = 26,783,115; prior GT captured only (b)(ii) ESOP component</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>other_nc_liabilities</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Other Noncurrent Liabilities_Other Long Term Liabilities</t>
+          <t>Authorised Equity Share Capital</t>
         </is>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>250</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>286,287,288,324,325,326</t>
+          <t>345</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2446,28 +2378,28 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>other_nc_liabilities</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Other Noncurrent Liabilities_Total Long Term Liabilities</t>
+          <t>Equity Issued</t>
         </is>
       </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,685</t>
+          <t>225</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>286,287,288,324,325,326</t>
+          <t>345</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2490,7 +2422,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>other_nc_liabilities</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2500,18 +2432,18 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Other Noncurrent Liabilities_Other Long Term Liabilities</t>
+          <t>Equity Subscribed fully paid</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>225</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>346,347,348,365,366,367</t>
+          <t>345</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2534,7 +2466,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>other_nc_liabilities</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2544,18 +2476,18 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Other Noncurrent Liabilities_Total Long Term Liabilities</t>
+          <t>Face Value of Share (in Rs)</t>
         </is>
       </c>
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>346,347,348,365,366,367</t>
+          <t>345</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2583,23 +2515,23 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Equity Forfeited</t>
+          <t>No Of Authorised Equity Shares</t>
         </is>
       </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>(546,249)</t>
+          <t>2,500,000,000</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>222,223,224,290,291,292</t>
+          <t>345</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2617,11 +2549,7 @@
           <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>p292 'Less: Face Value of Equity Shares forfeited (546,249)'</t>
-        </is>
-      </c>
+      <c r="J28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2631,42 +2559,38 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Equity Paid Up</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
+          <t>No Of Issued Equity Shares</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>2,247,780,169</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>222,223,224,290,291,292</t>
+          <t>345</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -2679,23 +2603,23 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>No Of Shares bought back or treasury shares</t>
+          <t>No Of Paid up Equity Shares</t>
         </is>
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>(26,783,115)</t>
+          <t>2,247,226,523</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>222,223,224,290,291,292</t>
+          <t>345</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2713,11 +2637,7 @@
           <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>p369 Less: Treasury Shares = (b)(i) 16,316,130 + (b)(ii) 10,466,985 = 26,783,115; prior GT captured only (b)(ii) ESOP component</t>
-        </is>
-      </c>
+      <c r="J30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2732,40 +2652,40 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Authorised Equity Share Capital</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
+          <t>No Of Shares bought back or treasury shares</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>(26,783,115)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>345,346</t>
+          <t>345</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>reconciled</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr"/>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>p292 Less: Treasury Shares = (b)(i) 16,316,130 + (b)(ii) 10,466,985 = 26,783,115</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2780,37 +2700,33 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Equity Issued</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
+          <t>No Of Subscribed Equity Shares Fully Paid</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>2,247,772,772</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>345,346</t>
+          <t>345</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>reconciled</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -2828,324 +2744,36 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Equity Subscribed fully paid</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
+          <t>Number of shares outstanding at beginning of period</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>2,220,623,508</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>345,346</t>
+          <t>345</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>reconciled</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>No Of Authorised Equity Shares</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2,220,000,000</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>2,500,000,000</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>345,346</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>reconciled</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>mismatch</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>No Of Issued Equity Shares</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2,220,000,000</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>2,247,780,169</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>345,346</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>reconciled</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>mismatch</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>No Of Paid up Equity Shares</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2,220,000,000</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>2,247,226,523</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>345,346</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>reconciled</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>mismatch</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>No Of Shares bought back or treasury shares</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>(26,783,115)</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>345,346</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>p292 Less: Treasury Shares = (b)(i) 16,316,130 + (b)(ii) 10,466,985 = 26,783,115</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>No Of Subscribed Equity Shares Fully Paid</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2,220,000,000</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>2,247,772,772</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>345,346</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>reconciled</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>mismatch</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Number of shares outstanding at beginning of period</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>2,220,623,508</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>345,346</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3158,7 +2786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3249,7 +2877,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>278,279,280,322,323,324</t>
+          <t>279,280,306,259,308,305,256,315</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -3297,7 +2925,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>193,194,195,225,226,227</t>
+          <t>194,204,205,206,162,172,164,170</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -3324,43 +2952,47 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>investment_property</t>
+          <t>finance_costs</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Gross Investment Property</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n"/>
+          <t>Interest Expense Borrowings</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12.91</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>408.54</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>258,259,260,261</t>
+          <t>192,169,168,162,170,237,199,204</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -3368,28 +3000,28 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>investment_property</t>
+          <t>investments</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Gross Investment Property</t>
+          <t>Non Current Investments_Joint Venture/Partnerships</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>505.45</t>
+          <t>146.42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>164,165,166,167</t>
+          <t>262,263,264</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3412,7 +3044,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>investments</t>
+          <t>loans_advances</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3422,33 +3054,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Non Current Investments_Joint Venture/Partnerships</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n"/>
+          <t>Short Term Loans And Advances_Other Deposit Assets</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25.24</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>146.42</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>262,263,264</t>
+          <t>280,256,335,297,278,400,366,328</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -3461,7 +3097,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -3469,7 +3105,11 @@
           <t>Short Term Loans And Advances_Other Deposit Assets</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21.89</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>6.26</t>
@@ -3477,22 +3117,22 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>279,280,281,36,37,38</t>
+          <t>227,162,235,183,200,221,182,409</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -3500,28 +3140,28 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>loans_advances</t>
+          <t>other_cur_liabilities</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Short Term Loans And Advances_Other Deposit Assets</t>
+          <t>Other Current Liabilities_Employees Stock Options Outstanding</t>
         </is>
       </c>
       <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>507.59</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>226,227,228,36,37,38</t>
+          <t>292,322,318,264,320,293,321,291</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3544,7 +3184,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>other_cur_liabilities</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -3554,33 +3194,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Other Current Liabilities_Employees Stock Options Outstanding</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n"/>
+          <t>CSR Expenditure</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>457.51</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>507.59</t>
+          <t>475.33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>291,292,293,327,328,329</t>
+          <t>297,256,259,280,335,279,265,421</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -3588,47 +3232,43 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>other_equity</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Hedging Reserve</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>31.84</t>
-        </is>
-      </c>
+          <t>Loss On Disposal Of Fixed Asset</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>(13.89)</t>
+          <t>(108.26)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>254,255,256,253</t>
+          <t>200,162,194,227,164,165,202,183</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -3641,501 +3281,41 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CSR Expenditure</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>457.51</t>
-        </is>
-      </c>
+          <t>Payments To Auditor</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>475.33</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>296,297,298,114,115,116</t>
+          <t>200,162,194,227,164,165,202,183</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>other_expenses</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Impairment loss on financial assets loans and advances</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>296,297,298,114,115,116</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>false_positive</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>other_expenses</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Loss On Disposal Of Fixed Asset</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>(138.76)</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>296,297,298,114,115,116</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>other_expenses</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Provision Bad Doubtful Loans Advances</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>296,297,298,114,115,116</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>p256 Consolidated Statement of Cash Flows 'Doubtful and bad advances, loans and deposits 1.95'</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>other_expenses</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Impairment loss on financial assets loans and advances</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>199,200,201,202,203</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>p162(pr.141): CF 'Doubtful and bad advances, loans and deposits 1.87'</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>other_expenses</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Loss On Disposal Of Fixed Asset</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>(108.26)</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>199,200,201,202,203</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>other_expenses</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Payments To Auditor</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>7.43</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>199,200,201,202,203</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>other_nc_liabilities</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Other Noncurrent Liabilities_Total Long Term Liabilities</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34.51</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>64,65,66,251,252,253</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>ppe</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation_Furnitures &amp; Fixtures</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>169.33</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>ppe</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation_Office Equipments</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>36.33</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>ppe</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Other CWIP</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>1087.60</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>unverified</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>false_positive</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4148,7 +3328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4218,7 +3398,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>deferred_tax</t>
+          <t>consolidated_equity</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -4228,12 +3408,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Deferred Tax Assets (Net)_Deferred tax liabilities_Accumulated Depreciation</t>
+          <t>Equity attributable to the equity holders of the parent</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>92,852</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -4243,7 +3423,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>328,329,330,331,332</t>
+          <t>289,287,34,291,293,17,344,290</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -4251,7 +3431,7 @@
           <t>grounded</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>false_positive</t>
         </is>
@@ -4266,22 +3446,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>investments</t>
+          <t>deferred_tax</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Non Current Investments_Unquoted Debentures/Bonds</t>
+          <t>Deferred Tax Assets (Net)_Deferred tax liabilities_Accumulated Depreciation</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>4,869</t>
+          <t>133</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -4291,15 +3471,15 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>236,237,238</t>
+          <t>332,303,301,302,77,298,295,329</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>unverified</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>false_positive</t>
         </is>
@@ -4314,7 +3494,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>loans_advances</t>
+          <t>other_cur_assets</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -4324,33 +3504,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Short Term Loans And Advances_Other Deposit Assets</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n"/>
+          <t>Other Current Assets_Advances given suppliers</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76,77,78,309,310,311</t>
+          <t>311,155,301,310,140,346,305,330</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -4358,43 +3542,47 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>loans_advances</t>
+          <t>other_equity</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Short Term Loans And Advances_Other Deposit Assets</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n"/>
+          <t>Share Premium</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1,091</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>203,204,205,206,207</t>
+          <t>321,290,292,291,293,312,37,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -4407,7 +3595,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -4415,30 +3603,34 @@
           <t>Hedging Reserve</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>(19)</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>(19)</t>
+          <t>(18)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>289,290,291,292,293</t>
+          <t>212,214,215,213,216,242,243,234</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -4451,7 +3643,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -4461,17 +3653,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>4,824</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,091</t>
+          <t>1,054</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>289,290,291,292,293</t>
+          <t>212,214,215,213,216,242,243,234</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4479,7 +3671,7 @@
           <t>grounded</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>mismatch</t>
         </is>
@@ -4494,43 +3686,47 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>other_equity</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Hedging Reserve</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n"/>
+          <t>Impairment loss on financial assets loans and advances</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>(18)</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211,212,213,214,215</t>
+          <t>301,337,329,320,295,67,332,311</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -4538,7 +3734,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>other_equity</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -4548,33 +3744,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Share Premium</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n"/>
+          <t>Payments To Auditor</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,054</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>211,212,213,214,215</t>
+          <t>257,258,259</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>reconciled</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -4587,50 +3787,50 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Bad Debts Advances Written Off</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n"/>
+          <t>Total Power &amp; Fuel Expenses</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>(270)</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>336,337,338</t>
+          <t>257,258,259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>reconciled</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>p320 'Amounts written off (270)'</t>
-        </is>
-      </c>
+          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>other_nc_liabilities</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -4640,37 +3840,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Impairment loss on financial assets loans and advances</t>
+          <t>Other Noncurrent Liabilities_Other Long Term Liabilities</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>4,332</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>336,337,338</t>
+          <t>287,304,339,35,328,329,343,141</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>grounded</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -4678,7 +3878,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>other_nc_liabilities</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -4688,12 +3888,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Payments To Auditor</t>
+          <t>Other Noncurrent Liabilities_Other Long Term Liabilities</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>495</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -4703,15 +3903,15 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>257,258,259</t>
+          <t>248,209,225,260,250,224,233,253</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>reconciled</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>false_positive</t>
         </is>
@@ -4726,47 +3926,43 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Total Power &amp; Fuel Expenses</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
+          <t>Authorised Equity Share Capital</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>257,258,259</t>
+          <t>324,325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>reconciled</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>false_positive</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -4774,7 +3970,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>other_nc_liabilities</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -4784,37 +3980,33 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Other Noncurrent Liabilities_Other Long Term Liabilities</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
+          <t>Equity Forfeited</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>₹1,500</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>328,329,330,338,339,340</t>
+          <t>324,325</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>false_positive</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -4822,47 +4014,43 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>other_nc_liabilities</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Other Noncurrent Liabilities_Other Long Term Liabilities</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
+          <t>Equity Issued</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>2,024</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>249,250,251,223,224,225</t>
+          <t>324,325</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>false_positive</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -4880,37 +4068,33 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>No Of Shares bought back or treasury shares</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>10,00,00,000</t>
-        </is>
-      </c>
+          <t>Equity Subscribed fully paid</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86,50,911</t>
+          <t>2,024</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>320,321,322,323</t>
+          <t>324,325</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -4928,18 +4112,18 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Number of shares outstanding at beginning of period</t>
+          <t>Face Value of Share (in Rs)</t>
         </is>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>414,36,07,528</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>320,321,322,323</t>
+          <t>324,325</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4967,42 +4151,38 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>No Of Subscribed Equity Shares Fully Paid</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>4,05,55,91,723</t>
-        </is>
-      </c>
+          <t>No Of Authorised Equity Shares</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>480,00,00,000</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>241,242,243,244</t>
+          <t>324,325</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>false_positive</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -5015,45 +4195,321 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>No Of Issued Equity Shares</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>404,69,40,812</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>324,325</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>share_capital</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>No Of Shares bought back or treasury shares</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10,00,00,000</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>86,50,911</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>324,325</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>reconciled</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Value mismatch — model extracted a different figure than the report</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>share_capital</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>No Of Subscribed Equity Shares Fully Paid</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>404,69,40,812</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>324,325</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>p324 'As at the end of the year 404,69,40,812'</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>share_capital</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Equity Issued</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2,027</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>241,242,243,244</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>share_capital</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Equity Subscribed fully paid</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2,027</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>241,242,243,244</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>share_capital</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>No Of Subscribed Equity Shares Fully Paid</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4,05,55,91,723</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>241,242,243,244</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>false_positive</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>share_capital</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Number of shares outstanding at beginning of period</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>4,15,32,63,455</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>241,242,243,244</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>grounded</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>false_positive</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5066,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5194,18 +4650,18 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Deferred Tax Assets (Net)_Deferred tax liabilities_Accumulated Depreciation</t>
+          <t>Deferred Tax Liability (Net)_Deferred Tax Assets_Leave Encashment</t>
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>4,614.21</t>
+          <t>94.32</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>310,311,312</t>
+          <t>310,326,297,346,304,305,285,283</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -5233,23 +4689,23 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Deferred Tax Liability (Net)_Deferred Tax Assets_Leave Encashment</t>
+          <t>Deferred Tax Assets (Net)_Deferred tax liabilities_Accumulated Depreciation</t>
         </is>
       </c>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94.32</t>
+          <t>308.32</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>310,311,312</t>
+          <t>260,254,234,247,235,231,246,240</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5293,7 +4749,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246,247,248</t>
+          <t>260,254,234,247,235,231,246,240</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5331,7 +4787,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,625.51</t>
+          <t>1625.51</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -5349,7 +4805,7 @@
           <t>reconciled</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>false_positive</t>
         </is>
@@ -5397,7 +4853,7 @@
           <t>unverified</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>mismatch</t>
         </is>
@@ -5445,7 +4901,7 @@
           <t>unverified</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>false_positive</t>
         </is>
@@ -5465,7 +4921,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -5476,12 +4932,12 @@
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>(4.84)</t>
+          <t>(2.43)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>312,313,314,385,386,387</t>
+          <t>249,226,248,260,255,251,268,227</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5504,55 +4960,55 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>loans_advances</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Short Term Loans And Advances_Advances to related parties</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20,287.52</t>
-        </is>
-      </c>
+          <t>Impairment loss on financial assets loans and advances</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>74.77</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>248,249,250,225,226,227</t>
+          <t>327,285,298,297,317,301,321,275</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>false_positive</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr"/>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>p327 'Allowances for Credit Loss / Doubtful advances 74.77'</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>loans_advances</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -5562,18 +5018,18 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Short Term Loans And Advances_Allowance for bad and doubtful loans</t>
+          <t>Loss On Disposal Of Fixed Asset</t>
         </is>
       </c>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>(2.43)</t>
+          <t>(9.63)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>248,249,250,225,226,227</t>
+          <t>255,256,257</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5591,33 +5047,37 @@
           <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>p231 'Loss/(Profit) on Sale/Disposal of PP&amp;E (9.63)'</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>other_cur_liabilities</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Other Current Liabilities_Revenue received in advance</t>
+          <t>Total Power &amp; Fuel Expenses</t>
         </is>
       </c>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,710.14</t>
+          <t>40.93</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>337,338,339</t>
+          <t>255,256,257</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5640,28 +5100,28 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>ppe</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Impairment loss on financial assets loans and advances</t>
+          <t>Accumulated Depreciation_Furnitures &amp; Fixtures</t>
         </is>
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>231.19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>255,256,257</t>
+          <t>305</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5679,85 +5139,81 @@
           <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>p255 'Allowances for Credit Loss / Doubtful advances 6.46'</t>
-        </is>
-      </c>
+      <c r="J13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>ppe</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Loss On Disposal Of Fixed Asset</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n"/>
+          <t>Accumulated Depreciation_Office Equipments</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>(9.63)</t>
+          <t>331.70</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>255,256,257</t>
+          <t>305</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>p231 'Loss/(Profit) on Sale/Disposal of PP&amp;E (9.63)'</t>
-        </is>
-      </c>
+          <t>Value mismatch — model extracted a different figure than the report</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>ppe</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Total Power &amp; Fuel Expenses</t>
+          <t>Gross Carrying Value_Furnitures &amp; Fixtures</t>
         </is>
       </c>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>1,180.71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>255,256,257</t>
+          <t>305</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5780,7 +5236,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>other_nc_liabilities</t>
+          <t>ppe</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -5790,33 +5246,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Other Noncurrent Liabilities_Other Long Term Liabilities</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n"/>
+          <t>Gross Carrying Value_Office Equipments</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,836.51</t>
+          <t>1,064.61</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>284,285,286,295,296,297</t>
+          <t>305</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -5824,28 +5284,28 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>other_nc_liabilities</t>
+          <t>ppe</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Other Noncurrent Liabilities_Total Long Term Liabilities</t>
+          <t>Accumulated Depreciation_Furnitures &amp; Fixtures</t>
         </is>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,836.51</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>284,285,286,295,296,297</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5868,7 +5328,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>other_nc_liabilities</t>
+          <t>ppe</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -5878,18 +5338,18 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Other Noncurrent Liabilities_Total Long Term Liabilities</t>
+          <t>Accumulated Depreciation_Office Equipments</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74.80</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>255,256,257,230,231,232</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5907,16 +5367,12 @@
           <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>p252 note25 'Other Non-Current Financial Liabilities 74.80' (Retention 1.85 + Interest accrued 72.95)</t>
-        </is>
-      </c>
+      <c r="J18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>pl_changes_inventory</t>
+          <t>ppe</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -5926,18 +5382,18 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Total Changes In Inventories Of Finished Goods, Work-In-Progress And Stock-In-Trade</t>
+          <t>Gross Carrying Value_Furnitures &amp; Fixtures</t>
         </is>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>(168.75)</t>
+          <t>60.62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>229,230,231,236,237,238</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5965,42 +5421,38 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation_Furnitures &amp; Fixtures</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>3,728.93</t>
-        </is>
-      </c>
+          <t>Gross Carrying Value_Office Equipments</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231.19</t>
+          <t>59.84</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>284,285,286,303,304,305</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -6008,7 +5460,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ppe</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -6018,37 +5470,33 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation_Office Equipments</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>411.91</t>
-        </is>
-      </c>
+          <t>Authorised Equity Share Capital</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>331.70</t>
+          <t>485.92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>284,285,286,303,304,305</t>
+          <t>315</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -6056,7 +5504,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ppe</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -6066,37 +5514,33 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Gross Carrying Value_Furnitures &amp; Fixtures</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>23,783.23</t>
-        </is>
-      </c>
+          <t>Equity Paid Up</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1,180.71</t>
+          <t>129.27</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>284,285,286,303,304,305</t>
+          <t>315</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -6104,7 +5548,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ppe</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -6114,37 +5558,33 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Gross Carrying Value_Office Equipments</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1,728.33</t>
-        </is>
-      </c>
+          <t>Equity Subscribed fully paid</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1,064.61</t>
+          <t>129.27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>284,285,286,303,304,305</t>
+          <t>315</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -6152,46 +5592,178 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>trade_payables</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Sundry Creditors</t>
+          <t>No Of Authorised Equity Shares</t>
         </is>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>4,85,92,00,000</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>share_capital</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>No Of Paid up Equity Shares</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1,29,26,82,416</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>share_capital</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>No Of Subscribed Equity Shares Fully Paid</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1,29,26,82,416</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>trade_payables</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Sundry Creditors</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>4,474.96</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>230,231</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>miss</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/error_report.xlsx
+++ b/error_report.xlsx
@@ -49,17 +49,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -499,13 +499,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
         <v>4</v>
-      </c>
-      <c r="D2" t="n">
-        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -518,16 +518,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -540,10 +540,10 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -575,16 +575,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -668,55 +668,59 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>deferred_tax</t>
+          <t>investments</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Deferred Tax Assets (Net)_Deferred tax liabilities_Accumulated Depreciation</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n"/>
+          <t>Non Current Investments_Joint Venture/Partnerships</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>1,498</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1,12,897</t>
+          <t>4,798</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>148,154,143,184,142,145,168,139</t>
+          <t>104,105,106</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>miss</t>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>p148 'Property, Plant and Equipment and ... 1,12,897'</t>
+          <t>p127-128: all JV holdings at cost excl debentures = JV equity [quoted Alok 269 + unquoted 979] + JV preference [Alok NCRPS 3,300 + Alok OCPS 250] = 4,798. Prior GT 3,300 captured only NCRPS preference, missing JV equity (1,248) and OCPS (250)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>deferred_tax</t>
+          <t>loans_advances</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -726,33 +730,37 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Deferred Tax Assets (Net)_Deferred tax liabilities_Accumulated Depreciation</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n"/>
+          <t>Short Term Loans And Advances_Advances to related parties</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>8,789</t>
+        </is>
+      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>37,535</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>101,114,113,100,103,110,102,97</t>
+          <t>95,120,108,113,121,33,110,109</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -760,28 +768,28 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>finance_costs</t>
+          <t>loans_advances</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Interest Expense Borrowings</t>
+          <t>Short Term Loans And Advances_Other Deposit Assets</t>
         </is>
       </c>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22,050</t>
+          <t>2,403</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>152,168,142,184,165,153,167,166</t>
+          <t>95,120,108,113,121,33,110,109</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -789,7 +797,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -804,107 +812,103 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>investments</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Non Current Investments_Unquoted Debentures/Bonds</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,084</t>
-        </is>
-      </c>
+          <t>Legal &amp; Professional Charges</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,105</t>
+          <t>3,874</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104,105,106</t>
+          <t>157,158</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>unverified</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>p127-128: unquoted debentures (excl subsidiaries) = JV-cos [BAM DLR Mumbai 40 + BAM DLR Network 2 + DXDC 63 = 105; Sintex Twenty Devind 900] + Other-co Mahan Energen 100 = 1,105. Prior GT 205 missed Sintex Twenty Devind 900</t>
+          <t>p157(pr.233): cons Other Expenses 'Professional Fees 3,874'</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>loans_advances</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Short Term Loans And Advances_Advances to related parties</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
+          <t>Legal &amp; Professional Charges</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>1,886</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148,158,153,149,159,33,162,144</t>
+          <t>101,113,120,117,102,85,132,93</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>false_positive</t>
+          <t>miss</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>p152 Establishment Expenses 'Professional Fees' = 1,886 = legal/professional/consultancy fees per definition (alias 'Professional and consultancy charges'). Prior 'Not disclosed' too strict</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>loans_advances</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -914,18 +918,18 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Short Term Loans And Advances_Other Deposit Assets</t>
+          <t>Total Power &amp; Fuel Expenses</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,403</t>
+          <t>19,735</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95,120,108,113,121,33,110,109</t>
+          <t>101,113,120,117,102,85,132,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -933,7 +937,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -944,290 +948,6 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>other_expenses</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Legal &amp; Professional Charges</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,874</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>157,158,148,153,145,144,143,136</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>p157(pr.233): cons Other Expenses 'Professional Fees 3,874'</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>other_expenses</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>CSR Expenditure</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,223</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>116,117</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>other_expenses</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Legal &amp; Professional Charges</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,886</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>116,117</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>p152 Establishment Expenses 'Professional Fees' = 1,886 = legal/professional/consultancy fees per definition (alias 'Professional and consultancy charges'). Prior 'Not disclosed' too strict</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>other_nc_liabilities</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Other Noncurrent Liabilities_Total Long Term Liabilities</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5,51,020</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6,932</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>169,183,184,139,154,152,143,148</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>mismatch</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>ppe</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation_Furnitures &amp; Fixtures</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>13,287</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6,717</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>unverified</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>mismatch</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>ppe</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation_Office Equipments</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>61,473</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22,187</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>unverified</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>mismatch</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1240,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1320,37 +1040,33 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Deferred Tax Assets (Net)_Deferred tax liabilities_Accumulated Depreciation</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>10,867</t>
-        </is>
-      </c>
+          <t>Deferred Tax Liability (Net)_Deferred Tax Assets_Leave Encashment</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>288,289,287,167,286,247,273,268</t>
+          <t>288,301,289,309,287,247,302,286</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -1358,7 +1074,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>deferred_tax</t>
+          <t>finance_costs</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1368,37 +1084,33 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Deferred Tax Assets (Net)_Deferred tax liabilities_Accumulated Depreciation</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>(5,751)</t>
-        </is>
-      </c>
+          <t>Interest Expense Borrowings</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>1,051</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>367,333,353,346,354,351,377,348</t>
+          <t>373,397,388,372,346,400,402,401</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>false_positive</t>
+          <t>miss</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -1406,28 +1118,28 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>finance_costs</t>
+          <t>investments</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Interest Expense Borrowings</t>
+          <t>Non Current Investments_Unquoted Debentures/Bonds</t>
         </is>
       </c>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,051</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>373,397,388,372,346,400,402,401</t>
+          <t>277,278,279,320,263</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1435,7 +1147,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -1455,7 +1167,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1463,30 +1175,34 @@
           <t>Non Current Investments_Joint Venture/Partnerships</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>277,278,279</t>
+          <t>357,358,359</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>miss</t>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -1494,7 +1210,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>investments</t>
+          <t>loans_advances</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1504,33 +1220,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Non Current Investments_Unquoted Debentures/Bonds</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n"/>
+          <t>Short Term Loans And Advances_Advances to related parties</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>277,278,279</t>
+          <t>278,322,284,238,330,290,285,316</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Model returned a value but GT says '-' — not disclosed in the report</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -1538,47 +1258,43 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>investments</t>
+          <t>other_cur_liabilities</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Non Current Investments_Joint Venture/Partnerships</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Other Current Liabilities_Revenue received in advance</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>358</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>357,358,359</t>
+          <t>313</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>unverified</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -1586,47 +1302,43 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>loans_advances</t>
+          <t>other_cur_liabilities</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Short Term Loans And Advances_Advances to related parties</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Other Current Liabilities_Revenue received in advance</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>278,322,284,238,330,290,285,316</t>
+          <t>385</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>false_positive</t>
+          <t>miss</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Model returned a value but GT says '-' — not disclosed in the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -1634,47 +1346,43 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>other_cur_assets</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Other Current Assets_Less : Doubtful Advances</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>(43)</t>
-        </is>
-      </c>
+          <t>Loss On Disposal Of Fixed Asset</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>(122)</t>
+          <t>(486)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>359,390,164,364,367,386,395,363</t>
+          <t>316,330,290,247,291,297,286,273</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>unverified</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -1682,7 +1390,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>other_cur_liabilities</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1692,18 +1400,18 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Other Current Liabilities_Revenue received in advance</t>
+          <t>Payment for reimbursement of expenses</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>316,330,290,247,291,297,286,273</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1711,7 +1419,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -1726,47 +1434,43 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>other_cur_liabilities</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Other Current Liabilities_Accrued Salary Payable</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
+          <t>Total Power &amp; Fuel Expenses</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>14,396</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>385,390,374,382,377,383,371,370</t>
+          <t>316,330,290,247,291,297,286,273</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>false_positive</t>
+          <t>miss</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1779,7 +1483,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1790,12 +1494,12 @@
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,062</t>
+          <t>1,006</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316,330,290,247,291,297,286,273</t>
+          <t>388,368,376,403,333,402,363,373</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1803,7 +1507,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -1823,23 +1527,23 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Loss On Disposal Of Fixed Asset</t>
+          <t>Total Power &amp; Fuel Expenses</t>
         </is>
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>(486)</t>
+          <t>8,798</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>316,330,290,247,291,297,286,273</t>
+          <t>388,368,376,403,333,402,363,373</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1847,7 +1551,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -1862,7 +1566,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>other_nc_liabilities</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1872,33 +1576,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Payment for reimbursement of expenses</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n"/>
+          <t>Other Noncurrent Liabilities_Other Long Term Liabilities</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1,685</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>316,330,290,247,291,297,286,273</t>
+          <t>325,295,329,257,326,313,289,270</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
+          <t>grounded</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>miss</t>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1906,7 +1614,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1916,18 +1624,18 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Total Power &amp; Fuel Expenses</t>
+          <t>Equity Forfeited</t>
         </is>
       </c>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,396</t>
+          <t>(546,249)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>316,330,290,247,291,297,286,273</t>
+          <t>291,292,293,222,223,224</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1935,7 +1643,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -1945,37 +1653,41 @@
           <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>p292 'Less: Face Value of Equity Shares forfeited (546,249)'</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>CSR Expenditure</t>
+          <t>No Of Paid up Equity Shares</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>2,220,443,408</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>2,247,226,523</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>388,368,376,403,333,402,363,373</t>
+          <t>291,292,293,222,223,224</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1983,7 +1695,7 @@
           <t>grounded</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>mismatch</t>
         </is>
@@ -1998,32 +1710,32 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>other_nc_liabilities</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Other Noncurrent Liabilities_Other Long Term Liabilities</t>
+          <t>Equity Forfeited</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,685</t>
+          <t>(546,249)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>325,295,329,257,326,313,289,270</t>
+          <t>368,369,370,394,395,396</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2033,12 +1745,12 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned a value but GT says '-' — not disclosed in the report</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -2046,7 +1758,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>other_nc_liabilities</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -2056,724 +1768,40 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Other Noncurrent Liabilities_Total Long Term Liabilities</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n"/>
+          <t>No Of Paid up Equity Shares</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2,220,443,408</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>2,247,226,523</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>367,396,403,372,397,401,343,351</t>
+          <t>368,369,370,394,395,396</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
+          <t>grounded</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>miss</t>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>ppe</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Gross Carrying Value_Office Equipments</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1,487</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1,467</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>reconciled</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>mismatch</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>ppe</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Other CWIP</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>27,023</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>reconciled</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>false_positive</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Equity Forfeited</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>(546,249)</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>222,223,224,290,291,292</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>p292 'Less: Face Value of Equity Shares forfeited (546,249)'</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Equity Paid Up</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>222,223,224,290,291,292</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>mismatch</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>No Of Shares bought back or treasury shares</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>(10,466,985)</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>(26,783,115)</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>222,223,224,290,291,292</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>mismatch</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>p369 Less: Treasury Shares = (b)(i) 16,316,130 + (b)(ii) 10,466,985 = 26,783,115; prior GT captured only (b)(ii) ESOP component</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Authorised Equity Share Capital</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Equity Issued</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Equity Subscribed fully paid</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Face Value of Share (in Rs)</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>No Of Authorised Equity Shares</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>2,500,000,000</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>No Of Issued Equity Shares</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>2,247,780,169</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>No Of Paid up Equity Shares</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>2,247,226,523</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>No Of Shares bought back or treasury shares</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>(26,783,115)</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>p292 Less: Treasury Shares = (b)(i) 16,316,130 + (b)(ii) 10,466,985 = 26,783,115</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>No Of Subscribed Equity Shares Fully Paid</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>2,247,772,772</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Number of shares outstanding at beginning of period</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>2,220,623,508</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2861,23 +1889,23 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Deferred Tax Liability (Net)_Deferred Tax Assets_Leave Encashment</t>
+          <t>Deferred Tax Assets (Net)_Deferred tax liabilities_Accumulated Depreciation</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>124.47</t>
+          <t>1501.96</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>279,280,306,259,308,305,256,315</t>
+          <t>169,204,206,205,203,164,193,207</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -2885,7 +1913,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -2897,7 +1925,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>p279 'On employees separation and retirement etc. ... 124.47'</t>
+          <t>p194 deferred-tax note, PP&amp;E/investment-property component closing 1501.96</t>
         </is>
       </c>
     </row>
@@ -2925,7 +1953,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>194,204,205,206,162,172,164,170</t>
+          <t>169,204,206,205,203,164,193,207</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -2933,7 +1961,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -2957,7 +1985,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2967,7 +1995,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -2977,7 +2005,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>192,169,168,162,170,237,199,204</t>
+          <t>290,263,257,297,265,256,325,306</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2985,7 +2013,7 @@
           <t>grounded</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>false_positive</t>
         </is>
@@ -3000,7 +2028,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>investments</t>
+          <t>loans_advances</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3010,33 +2038,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Non Current Investments_Joint Venture/Partnerships</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n"/>
+          <t>Short Term Loans And Advances_Other Deposit Assets</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25.24</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>146.42</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>262,263,264</t>
+          <t>280,256,335,297,278,400,366,328</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
+          <t>grounded</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>miss</t>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -3049,7 +2081,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -3059,7 +2091,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25.24</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -3069,7 +2101,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>280,256,335,297,278,400,366,328</t>
+          <t>227,162,235,183,200,221,182,409</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3077,7 +2109,7 @@
           <t>grounded</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>mismatch</t>
         </is>
@@ -3092,47 +2124,43 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>loans_advances</t>
+          <t>other_cur_liabilities</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Short Term Loans And Advances_Other Deposit Assets</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>21.89</t>
-        </is>
-      </c>
+          <t>Other Current Liabilities_Employees Stock Options Outstanding</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>507.59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>227,162,235,183,200,221,182,409</t>
+          <t>292,322,318,264,320,293,321,291</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -3140,7 +2168,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>other_cur_liabilities</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3150,33 +2178,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Other Current Liabilities_Employees Stock Options Outstanding</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n"/>
+          <t>CSR Expenditure</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>457.51</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>507.59</t>
+          <t>475.33</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>292,322,318,264,320,293,321,291</t>
+          <t>297,256,259,280,335,279,265,421</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
+          <t>grounded</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>miss</t>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -3194,17 +2226,13 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>CSR Expenditure</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>457.51</t>
-        </is>
-      </c>
+          <t>Loss On Disposal Of Fixed Asset</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>475.33</t>
+          <t>(138.76)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -3214,17 +2242,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -3242,13 +2270,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Loss On Disposal Of Fixed Asset</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n"/>
+          <t>Payments To Auditor</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17.43</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>(108.26)</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -3258,17 +2290,17 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
+          <t>grounded</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>miss</t>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -3286,13 +2318,13 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Payments To Auditor</t>
+          <t>Provision Bad Doubtful Loans Advances</t>
         </is>
       </c>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3305,7 +2337,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -3315,7 +2347,11 @@
           <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>p162 'Doubtful and bad advances, loans and deposits 1.87'</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3328,7 +2364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3398,7 +2434,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>consolidated_equity</t>
+          <t>other_cur_assets</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3408,60 +2444,60 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Equity attributable to the equity holders of the parent</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>92,852</t>
-        </is>
-      </c>
+          <t>Other Current Assets_Advances given suppliers</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>474</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>289,287,34,291,293,17,344,290</t>
+          <t>311,155,301,310,140,346,305,330</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>false_positive</t>
+          <t>miss</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>p311 note 2.10: 'Payment to vendors for supply of goods 474 413' — matches alias 'Advance to vendors'; prior GT 'Not disclosed' wrong</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>deferred_tax</t>
+          <t>other_cur_assets</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Deferred Tax Assets (Net)_Deferred tax liabilities_Accumulated Depreciation</t>
+          <t>Other Current Assets_Advances given suppliers</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>408</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -3471,7 +2507,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>332,303,301,302,77,298,295,329</t>
+          <t>233,204,220,232,223,271,263,251</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -3479,7 +2515,7 @@
           <t>grounded</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>false_positive</t>
         </is>
@@ -3494,32 +2530,32 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>other_cur_assets</t>
+          <t>other_equity</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Other Current Assets_Advances given suppliers</t>
+          <t>Share Premium</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>1,539</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>243</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>311,155,301,310,140,346,305,330</t>
+          <t>212,214,215,213,216,242,243,234</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3527,22 +2563,26 @@
           <t>grounded</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>false_positive</t>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>Value mismatch — model extracted a different figure than the report</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>FY2026 SOCIE closing (p216) = 243; prior GT 1,054 was FY2025 closing / FY2026 opening (p213/p214)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>other_equity</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3552,78 +2592,78 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Share Premium</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
+          <t>Bad Debts Advances Written Off</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,091</t>
+          <t>(270)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>321,290,292,291,293,312,37,35</t>
+          <t>337</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>p320 'Amounts written off (270)'</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>other_equity</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Hedging Reserve</t>
+          <t>Impairment loss on financial assets loans and advances</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>(19)</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>(18)</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>212,214,215,213,216,242,243,234</t>
+          <t>337</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>unverified</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
+          <t>reconciled</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>mismatch</t>
         </is>
@@ -3638,47 +2678,47 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>other_equity</t>
+          <t>other_nc_liabilities</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Share Premium</t>
+          <t>Other Noncurrent Liabilities_Other Long Term Liabilities</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,824</t>
+          <t>561</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,054</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>212,214,215,213,216,242,243,234</t>
+          <t>287,288</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
+          <t>reconciled</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -3686,47 +2726,47 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>other_nc_liabilities</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Impairment loss on financial assets loans and advances</t>
+          <t>Other Noncurrent Liabilities_Other Long Term Liabilities</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>495</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>301,337,329,320,295,67,332,311</t>
+          <t>209</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>reconciled</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -3734,47 +2774,43 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Payments To Auditor</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Authorised Equity Share Capital</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>257,258,259</t>
+          <t>321,322,323,320</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>reconciled</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>false_positive</t>
+          <t>miss</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -3782,47 +2818,43 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Total Power &amp; Fuel Expenses</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
+          <t>Equity Forfeited</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>₹1,500</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>257,258,259</t>
+          <t>321,322,323,320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>reconciled</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>false_positive</t>
+          <t>miss</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -3830,7 +2862,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>other_nc_liabilities</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -3840,37 +2872,33 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Other Noncurrent Liabilities_Other Long Term Liabilities</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4,332</t>
-        </is>
-      </c>
+          <t>Equity Issued</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>2,024</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>287,304,339,35,328,329,343,141</t>
+          <t>321,322,323,320</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>false_positive</t>
+          <t>miss</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -3878,47 +2906,43 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>other_nc_liabilities</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Other Noncurrent Liabilities_Other Long Term Liabilities</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
+          <t>Equity Paid Up</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>2,024</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>248,209,225,260,250,224,233,253</t>
+          <t>321,322,323,320</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>grounded</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>false_positive</t>
+          <t>miss</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -3936,18 +2960,18 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Authorised Equity Share Capital</t>
+          <t>Equity Subscribed fully paid</t>
         </is>
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,024</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>324,325</t>
+          <t>321,322,323,320</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3955,7 +2979,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -3980,18 +3004,18 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Equity Forfeited</t>
+          <t>Face Value of Share (in Rs)</t>
         </is>
       </c>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>₹1,500</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>324,325</t>
+          <t>321,322,323,320</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3999,7 +3023,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -4024,18 +3048,18 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Equity Issued</t>
+          <t>No Of Authorised Equity Shares</t>
         </is>
       </c>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,024</t>
+          <t>480,00,00,000</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>324,325</t>
+          <t>321,322,323,320</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4043,7 +3067,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -4068,18 +3092,18 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Equity Subscribed fully paid</t>
+          <t>No Of Issued Equity Shares</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,024</t>
+          <t>404,69,40,812</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>324,325</t>
+          <t>321,322,323,320</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4087,7 +3111,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -4112,18 +3136,18 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Face Value of Share (in Rs)</t>
+          <t>No Of Paid up Equity Shares</t>
         </is>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>404,69,40,812</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>324,325</t>
+          <t>321,322,323,320</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4131,7 +3155,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -4141,7 +3165,11 @@
           <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>p324 'As at the end of the year 404,69,40,812'</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4156,18 +3184,18 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>No Of Authorised Equity Shares</t>
+          <t>No Of Shares bought back or treasury shares</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>480,00,00,000</t>
+          <t>86,50,911</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>324,325</t>
+          <t>321,322,323,320</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4175,7 +3203,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -4200,7 +3228,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>No Of Issued Equity Shares</t>
+          <t>No Of Subscribed Equity Shares Fully Paid</t>
         </is>
       </c>
       <c r="D19" s="2" t="n"/>
@@ -4211,7 +3239,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>324,325</t>
+          <t>321,322,323,320</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4219,7 +3247,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -4229,7 +3257,11 @@
           <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>p324 'As at the end of the year 404,69,40,812'</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4244,272 +3276,36 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>No Of Shares bought back or treasury shares</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>10,00,00,000</t>
-        </is>
-      </c>
+          <t>Number of shares outstanding at beginning of period</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>86,50,911</t>
+          <t>414,36,07,528</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>324,325</t>
+          <t>321,322,323,320</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>reconciled</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>No Of Subscribed Equity Shares Fully Paid</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>404,69,40,812</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>324,325</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>p324 'As at the end of the year 404,69,40,812'</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Equity Issued</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2,027</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>241,242,243,244</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Equity Subscribed fully paid</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>2,027</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>241,242,243,244</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>No Of Subscribed Equity Shares Fully Paid</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>4,05,55,91,723</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>241,242,243,244</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>false_positive</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Number of shares outstanding at beginning of period</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>4,15,32,63,455</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>241,242,243,244</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>grounded</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>false_positive</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4522,7 +3318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4592,55 +3388,55 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>borrowings</t>
+          <t>finance_costs</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Noncurrent Borrowings_Unsecured Loans_Loans and advances from others</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n"/>
+          <t>Interest Expense Borrowings</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>1,625.51</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>9,726.16</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>317,318</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>reconciled</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>p316 note23 Non-Current Borrowings UNSECURED 'Inter Corporate Loans 9,726.16'</t>
-        </is>
-      </c>
+          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>deferred_tax</t>
+          <t>investments</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -4650,33 +3446,37 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Deferred Tax Liability (Net)_Deferred Tax Assets_Leave Encashment</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n"/>
+          <t>Non Current Investments_Joint Venture/Partnerships</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>94.32</t>
+          <t>6,705.74</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>310,326,297,346,304,305,285,283</t>
+          <t>308,309,310,283,349</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>miss</t>
+          <t>mismatch</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Value mismatch — model extracted a different figure than the report</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -4684,7 +3484,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>deferred_tax</t>
+          <t>investments</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -4694,33 +3494,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Deferred Tax Assets (Net)_Deferred tax liabilities_Accumulated Depreciation</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n"/>
+          <t>Non Current Investments_Joint Venture/Partnerships</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>308.32</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>260,254,234,247,235,231,246,240</t>
+          <t>245,246,247</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
+          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -4728,28 +3532,28 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>deferred_tax</t>
+          <t>loans_advances</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Deferred Tax Liability (Net)_Deferred Tax Assets_Leave Encashment</t>
+          <t>Short Term Loans And Advances_Allowance for bad and doubtful loans</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>(4.84)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>260,254,234,247,235,231,246,240</t>
+          <t>313,314,285,327,379,324,386,309</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4757,7 +3561,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -4772,7 +3576,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>finance_costs</t>
+          <t>loans_advances</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -4782,12 +3586,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Interest Expense Borrowings</t>
+          <t>Short Term Loans And Advances_Advances to related parties</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1625.51</t>
+          <t>20,287.52</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -4797,15 +3601,15 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>249,226,248,260,255,251,268,227</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>reconciled</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
+          <t>grounded</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>false_positive</t>
         </is>
@@ -4820,47 +3624,43 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>investments</t>
+          <t>loans_advances</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Non Current Investments_Joint Venture/Partnerships</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
+          <t>Short Term Loans And Advances_Allowance for bad and doubtful loans</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,705.74</t>
+          <t>(2.43)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>308,309,310</t>
+          <t>249,226,248,260,255,251,268,227</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>unverified</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>mismatch</t>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>miss</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -4868,47 +3668,43 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>investments</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Non Current Investments_Joint Venture/Partnerships</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Bad Debts Advances Written Off</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>206.68</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>245,246,247</t>
+          <t>327,285,298,297,317,301,321,275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>false_positive</t>
+          <t>miss</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
+          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -4916,7 +3712,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>loans_advances</t>
+          <t>other_expenses</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -4926,18 +3722,18 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Short Term Loans And Advances_Allowance for bad and doubtful loans</t>
+          <t>Impairment loss on financial assets loans and advances</t>
         </is>
       </c>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>(2.43)</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>249,226,248,260,255,251,268,227</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4945,7 +3741,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -4955,7 +3751,11 @@
           <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>p255 'Allowances for Credit Loss / Doubtful advances 6.46'</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -4965,23 +3765,23 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Impairment loss on financial assets loans and advances</t>
+          <t>Loss On Disposal Of Fixed Asset</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74.77</t>
+          <t>(9.63)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>327,285,298,297,317,301,321,275</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4989,7 +3789,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -5001,7 +3801,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>p327 'Allowances for Credit Loss / Doubtful advances 74.77'</t>
+          <t>p231 'Loss/(Profit) on Sale/Disposal of PP&amp;E (9.63)'</t>
         </is>
       </c>
     </row>
@@ -5018,18 +3818,18 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Loss On Disposal Of Fixed Asset</t>
+          <t>Total Power &amp; Fuel Expenses</t>
         </is>
       </c>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>(9.63)</t>
+          <t>40.93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>255,256,257</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5037,7 +3837,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -5047,16 +3847,12 @@
           <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>p231 'Loss/(Profit) on Sale/Disposal of PP&amp;E (9.63)'</t>
-        </is>
-      </c>
+      <c r="J11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>other_expenses</t>
+          <t>other_nc_liabilities</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -5066,18 +3862,18 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Total Power &amp; Fuel Expenses</t>
+          <t>Other Noncurrent Liabilities_Total Long Term Liabilities</t>
         </is>
       </c>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>74.80</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>255,256,257</t>
+          <t>256,239,238,252,257,230,274,232</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,7 +3881,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -5095,33 +3891,37 @@
           <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>p252 note25 'Other Non-Current Financial Liabilities 74.80' (Retention 1.85 + Interest accrued 72.95)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ppe</t>
+          <t>pl_changes_inventory</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation_Furnitures &amp; Fixtures</t>
+          <t>Total Changes In Inventories Of Finished Goods, Work-In-Progress And Stock-In-Trade</t>
         </is>
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>231.19</t>
+          <t>(168.75)</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>237,255,223,231,230,248,233,234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5129,7 +3929,7 @@
           <t>absent</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
@@ -5144,7 +3944,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ppe</t>
+          <t>share_capital</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -5154,616 +3954,40 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation_Office Equipments</t>
+          <t>Equity Forfeited</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>(0.03)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>331.70</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>313,314,315,366,367,368</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>grounded</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
+          <t>Model returned a value but GT says 'Not disclosed' — not disclosed in the report</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>ppe</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Gross Carrying Value_Furnitures &amp; Fixtures</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1,180.71</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>ppe</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Gross Carrying Value_Office Equipments</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2,13</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,064.61</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>unverified</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>mismatch</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Value mismatch — model extracted a different figure than the report</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>ppe</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation_Furnitures &amp; Fixtures</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>25.26</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>ppe</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation_Office Equipments</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>38.49</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>ppe</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Gross Carrying Value_Furnitures &amp; Fixtures</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>60.62</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>ppe</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Gross Carrying Value_Office Equipments</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>59.84</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Authorised Equity Share Capital</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>485.92</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Equity Paid Up</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>129.27</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Equity Subscribed fully paid</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>129.27</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>No Of Authorised Equity Shares</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>4,85,92,00,000</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>No Of Paid up Equity Shares</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1,29,26,82,416</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>No Of Subscribed Equity Shares Fully Paid</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>1,29,26,82,416</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>trade_payables</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Sundry Creditors</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>4,474.96</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>absent</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>miss</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Model returned ABSENT — datapoint not located/extracted (locate or extraction gap)</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
